--- a/appendix/역전파와_ReLU_기울기소실_정리.xlsx
+++ b/appendix/역전파와_ReLU_기울기소실_정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\조근하\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18811174-2446-4664-A097-E2141FD11072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEDBCCB2-F9C9-4FB7-ACF7-32726249246F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -389,7 +389,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -457,13 +457,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF00B0F0"/>
-      <name val="D2Coding"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF00B0F0"/>
       <name val="D2Coding"/>
@@ -661,7 +654,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -765,9 +758,6 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="5" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -790,12 +780,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="9" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1591,7 +1575,7 @@
       <c r="D12" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="43" t="s">
         <v>110</v>
       </c>
       <c r="F12" s="39" t="s">
@@ -1611,14 +1595,14 @@
       <c r="C13" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="51">
+      <c r="D13" s="40">
         <f>C6*C5</f>
         <v>6</v>
       </c>
-      <c r="E13" s="45" t="s">
+      <c r="E13" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="50">
+      <c r="F13" s="40">
         <f>C6*C5</f>
         <v>6</v>
       </c>
@@ -1636,14 +1620,14 @@
       <c r="C14" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="47">
         <f>1/(1+EXP(-D13))</f>
         <v>0.99752737684336534</v>
       </c>
-      <c r="E14" s="46" t="s">
+      <c r="E14" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="48">
         <f>MAX(0, F13)</f>
         <v>6</v>
       </c>
@@ -1665,7 +1649,7 @@
         <f>C7*D14</f>
         <v>1.9950547536867307</v>
       </c>
-      <c r="E15" s="45" t="s">
+      <c r="E15" s="44" t="s">
         <v>78</v>
       </c>
       <c r="F15" s="40">
@@ -1686,14 +1670,14 @@
       <c r="C16" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="41">
         <f>0.5*(D15-C8)^2</f>
         <v>32.039574198236707</v>
       </c>
-      <c r="E16" s="47" t="s">
+      <c r="E16" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="F16" s="42">
+      <c r="F16" s="41">
         <f>0.5*(F15-C8)^2</f>
         <v>2</v>
       </c>
@@ -1715,7 +1699,7 @@
         <f>D15-C8</f>
         <v>-8.0049452463132695</v>
       </c>
-      <c r="E17" s="45" t="s">
+      <c r="E17" s="44" t="s">
         <v>86</v>
       </c>
       <c r="F17" s="40">
@@ -1736,14 +1720,14 @@
       <c r="C18" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="48">
+      <c r="D18" s="47">
         <f>D14*(1-D14)</f>
         <v>2.4665092913599309E-3</v>
       </c>
-      <c r="E18" s="46" t="s">
+      <c r="E18" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="F18" s="49">
+      <c r="F18" s="48">
         <f>IF(F13&gt;0, 1, 0)</f>
         <v>1</v>
       </c>
@@ -1761,14 +1745,14 @@
       <c r="C19" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="48">
+      <c r="D19" s="47">
         <f>D17*C7*D18*C5</f>
         <v>-7.8977087307436758E-2</v>
       </c>
-      <c r="E19" s="46" t="s">
+      <c r="E19" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="F19" s="49">
+      <c r="F19" s="48">
         <f>F17*C7*F18*C5</f>
         <v>8</v>
       </c>
@@ -1786,14 +1770,14 @@
       <c r="C20" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="42">
         <f>C6-C9*D19</f>
         <v>3.0007897708730744</v>
       </c>
-      <c r="E20" s="47" t="s">
+      <c r="E20" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="F20" s="43">
+      <c r="F20" s="42">
         <f>C6-C9*F19</f>
         <v>2.92</v>
       </c>
